--- a/output/stock_quant_scores/AMD_balance_df.xlsx
+++ b/output/stock_quant_scores/AMD_balance_df.xlsx
@@ -1707,24 +1707,34 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>661000000</v>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>4343000000</v>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>7497000000</v>
+      </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
+      <c r="R6" t="n">
+        <v>-1451000000</v>
+      </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>4922000000</v>
+      </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
@@ -1732,7 +1742,9 @@
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
+      <c r="AD6" t="n">
+        <v>4240000000</v>
+      </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
@@ -1745,7 +1757,9 @@
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="inlineStr"/>
+      <c r="AQ6" t="n">
+        <v>12419000000</v>
+      </c>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
@@ -1774,12 +1788,16 @@
       </c>
       <c r="BJ6" t="inlineStr"/>
       <c r="BK6" t="inlineStr"/>
-      <c r="BL6" t="inlineStr"/>
+      <c r="BL6" t="n">
+        <v>8583000000</v>
+      </c>
       <c r="BM6" t="inlineStr"/>
       <c r="BN6" t="n">
         <v>378000000</v>
       </c>
-      <c r="BO6" t="inlineStr"/>
+      <c r="BO6" t="n">
+        <v>1955000000</v>
+      </c>
       <c r="BP6" t="inlineStr"/>
       <c r="BQ6" t="inlineStr"/>
       <c r="BR6" t="inlineStr"/>
@@ -1789,7 +1807,9 @@
       <c r="BV6" t="inlineStr"/>
       <c r="BW6" t="inlineStr"/>
       <c r="BX6" t="inlineStr"/>
-      <c r="BY6" t="inlineStr"/>
+      <c r="BY6" t="n">
+        <v>2535000000</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
